--- a/Tabels/Tables.xlsx
+++ b/Tabels/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isaacguediri/GNS3 Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isaacguediri/GNS3 Project/Tabels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F87E7904-C144-4844-B490-FACA255EB021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6044069-7751-054C-8720-3AE37A6A94DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15200" yWindow="9600" windowWidth="15040" windowHeight="8480" xr2:uid="{7F52C480-538E-5449-83C7-A9380CDCB259}"/>
+    <workbookView xWindow="15140" yWindow="660" windowWidth="15100" windowHeight="17660" activeTab="1" xr2:uid="{7F52C480-538E-5449-83C7-A9380CDCB259}"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
   <si>
     <t>Department</t>
   </si>
@@ -52,18 +52,9 @@
     <t>Subnet &amp; Mask</t>
   </si>
   <si>
-    <t>Defaut Gateway</t>
-  </si>
-  <si>
     <t>Management</t>
   </si>
   <si>
-    <t>10.0.99.0/30</t>
-  </si>
-  <si>
-    <t>10.0.99.2</t>
-  </si>
-  <si>
     <t>HR</t>
   </si>
   <si>
@@ -76,45 +67,12 @@
     <t>Servers</t>
   </si>
   <si>
-    <t>10.0.10.0/27</t>
-  </si>
-  <si>
-    <t>10.0.20.0/27</t>
-  </si>
-  <si>
     <t>10.0.40.0/24</t>
   </si>
   <si>
-    <t>10.0.30.0/27</t>
-  </si>
-  <si>
-    <t>10.0.10.30</t>
-  </si>
-  <si>
-    <t>10.0.20.30</t>
-  </si>
-  <si>
-    <t>10.0.30.30</t>
-  </si>
-  <si>
     <t>10.0.40.254</t>
   </si>
   <si>
-    <t>99.99.99.99/32</t>
-  </si>
-  <si>
-    <t>10.10.10.10/32</t>
-  </si>
-  <si>
-    <t>20.20.20.20/32</t>
-  </si>
-  <si>
-    <t>30.30.30.30/32</t>
-  </si>
-  <si>
-    <t>40.40.40.40/32</t>
-  </si>
-  <si>
     <t>IP Address</t>
   </si>
   <si>
@@ -167,6 +125,144 @@
   </si>
   <si>
     <t>198.51.100.0/30</t>
+  </si>
+  <si>
+    <t>Router's IP</t>
+  </si>
+  <si>
+    <t>Switch's IP</t>
+  </si>
+  <si>
+    <t>10.10.100.1</t>
+  </si>
+  <si>
+    <t>10.10.100.2</t>
+  </si>
+  <si>
+    <t>10.10.100.5</t>
+  </si>
+  <si>
+    <t>10.10.100.6</t>
+  </si>
+  <si>
+    <t>10.10.100.9</t>
+  </si>
+  <si>
+    <t>10.10.100.10</t>
+  </si>
+  <si>
+    <t>10.10.100.13</t>
+  </si>
+  <si>
+    <t>10.10.100.14</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>203.0.113.1</t>
+  </si>
+  <si>
+    <t>198.51.100.1</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>50.50.50.50/32</t>
+  </si>
+  <si>
+    <t>60.60.60.60/32</t>
+  </si>
+  <si>
+    <t>70.70.70.70/32</t>
+  </si>
+  <si>
+    <t>80.80.80.80/32</t>
+  </si>
+  <si>
+    <t>10.0.99.0/24</t>
+  </si>
+  <si>
+    <t>10.0.99.254</t>
+  </si>
+  <si>
+    <t>10.0.10.0/24</t>
+  </si>
+  <si>
+    <t>10.0.20.0/24</t>
+  </si>
+  <si>
+    <t>10.0.30.0/24</t>
+  </si>
+  <si>
+    <t>10.0.10.254</t>
+  </si>
+  <si>
+    <t>10.0.20.254</t>
+  </si>
+  <si>
+    <t>10.0.30.254</t>
+  </si>
+  <si>
+    <t>Virtual Defaut Gateway</t>
+  </si>
+  <si>
+    <t>DHCP Server</t>
+  </si>
+  <si>
+    <t>10.0.30.1</t>
+  </si>
+  <si>
+    <t>HR (SVI)</t>
+  </si>
+  <si>
+    <t>IT (SVI)</t>
+  </si>
+  <si>
+    <t>Marketing (SVI)</t>
+  </si>
+  <si>
+    <t>Servers (SVI)</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>isaac</t>
+  </si>
+  <si>
+    <t>gns3</t>
+  </si>
+  <si>
+    <t>secret</t>
+  </si>
+  <si>
+    <t>domain name</t>
+  </si>
+  <si>
+    <t>gns3project.com</t>
+  </si>
+  <si>
+    <t>10.0.99.10</t>
+  </si>
+  <si>
+    <t>10.0.99.20</t>
+  </si>
+  <si>
+    <t>10.0.99.30</t>
+  </si>
+  <si>
+    <t>10.0.99.40</t>
   </si>
 </sst>
 </file>
@@ -547,13 +643,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADD75ECA-A6D1-114F-978B-6EBEE10107EB}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="19.1640625" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -567,77 +663,85 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -647,11 +751,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51889FE0-C994-8F40-8D48-AC943DACFC35}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -659,47 +763,95 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -709,88 +861,131 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB6E3D7-0E19-7546-895E-C5BCE8FD9AE6}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Tabels/Tables.xlsx
+++ b/Tabels/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isaacguediri/GNS3 Project/Tabels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6044069-7751-054C-8720-3AE37A6A94DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E1AA09-B2EB-EB4B-ADF5-7E5C1DBB6B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15140" yWindow="660" windowWidth="15100" windowHeight="17660" activeTab="1" xr2:uid="{7F52C480-538E-5449-83C7-A9380CDCB259}"/>
+    <workbookView xWindow="15140" yWindow="660" windowWidth="15100" windowHeight="17580" activeTab="1" xr2:uid="{7F52C480-538E-5449-83C7-A9380CDCB259}"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN" sheetId="1" r:id="rId1"/>

--- a/Tabels/Tables.xlsx
+++ b/Tabels/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isaacguediri/GNS3 Project/Tabels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E1AA09-B2EB-EB4B-ADF5-7E5C1DBB6B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE57DE6-5E94-C04E-A8D2-8975E69150AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15140" yWindow="660" windowWidth="15100" windowHeight="17580" activeTab="1" xr2:uid="{7F52C480-538E-5449-83C7-A9380CDCB259}"/>
+    <workbookView xWindow="15140" yWindow="660" windowWidth="15100" windowHeight="17580" xr2:uid="{7F52C480-538E-5449-83C7-A9380CDCB259}"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
   <si>
     <t>Department</t>
   </si>
@@ -94,27 +94,12 @@
     <t>R2⟷D2</t>
   </si>
   <si>
-    <t>R1⟷ISP1</t>
-  </si>
-  <si>
-    <t>R2⟷ISP2</t>
-  </si>
-  <si>
     <t>OSPF Area 0</t>
   </si>
   <si>
-    <t>BGP (AS 65001 ↔ AS 65100)</t>
-  </si>
-  <si>
-    <t>BGP (AS 65001 ↔ AS 65200)</t>
-  </si>
-  <si>
     <t>10.10.100.0/30</t>
   </si>
   <si>
-    <t>203.0.113.0/30</t>
-  </si>
-  <si>
     <t>10.10.100.4/30</t>
   </si>
   <si>
@@ -124,9 +109,6 @@
     <t>10.10.100.12/30</t>
   </si>
   <si>
-    <t>198.51.100.0/30</t>
-  </si>
-  <si>
     <t>Router's IP</t>
   </si>
   <si>
@@ -157,15 +139,6 @@
     <t>10.10.100.14</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>203.0.113.1</t>
-  </si>
-  <si>
-    <t>198.51.100.1</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -178,18 +151,6 @@
     <t>D2</t>
   </si>
   <si>
-    <t>50.50.50.50/32</t>
-  </si>
-  <si>
-    <t>60.60.60.60/32</t>
-  </si>
-  <si>
-    <t>70.70.70.70/32</t>
-  </si>
-  <si>
-    <t>80.80.80.80/32</t>
-  </si>
-  <si>
     <t>10.0.99.0/24</t>
   </si>
   <si>
@@ -263,6 +224,18 @@
   </si>
   <si>
     <t>10.0.99.40</t>
+  </si>
+  <si>
+    <t>50.50.50.50</t>
+  </si>
+  <si>
+    <t>60.60.60.60</t>
+  </si>
+  <si>
+    <t>70.70.70.70</t>
+  </si>
+  <si>
+    <t>80.80.80.80</t>
   </si>
 </sst>
 </file>
@@ -663,7 +636,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -674,10 +647,10 @@
         <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -688,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -702,10 +675,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -716,10 +689,10 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -738,10 +711,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -768,90 +741,90 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +839,7 @@
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -880,10 +853,10 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -891,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -908,16 +881,16 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -925,16 +898,16 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -942,51 +915,23 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
